--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2017,6 +2017,2077 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129753892</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>667814</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6700444</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129753856</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>667802</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6700466</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129753891</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>667765</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6700434</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129753895</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>667848</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6700386</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129753871</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96210</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>210</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>667785</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6700459</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129753859</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98746</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>667807</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6700432</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129753893</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>667832</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6700425</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129753851</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>667791</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6700469</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129753860</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98746</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>667843</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6700368</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129753890</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>667791</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6700438</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129753866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>667834</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6700417</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129753867</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>667764</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6700442</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129753870</v>
+      </c>
+      <c r="B26" t="n">
+        <v>75187</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>667799</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6700409</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129753873</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>667793</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6700438</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129753845</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101864</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>667823</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6700429</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129753854</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>667811</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6700403</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129753874</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>667806</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6700465</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129753896</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100957</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>667762</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6700443</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129753868</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>667748</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6700464</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129753872</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>667802</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6700434</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>100957</v>
+        <v>97015</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R20" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,6 +2702,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2718,32 +2733,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>97014</v>
+        <v>100958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R21" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2799,21 +2814,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,54 +3024,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753866</v>
+        <v>129753870</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>75188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667834</v>
+        <v>667799</v>
       </c>
       <c r="R24" t="n">
-        <v>6700417</v>
+        <v>6700409</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3114,6 +3105,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3130,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753867</v>
+        <v>129753866</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3166,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3174,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667764</v>
+        <v>667834</v>
       </c>
       <c r="R25" t="n">
-        <v>6700442</v>
+        <v>6700417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3236,45 +3242,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753870</v>
+        <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>75187</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667799</v>
+        <v>667764</v>
       </c>
       <c r="R26" t="n">
-        <v>6700409</v>
+        <v>6700442</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3317,21 +3332,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3463,7 +3463,7 @@
         <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>129753854</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>129753868</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -3024,45 +3024,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753870</v>
+        <v>129753866</v>
       </c>
       <c r="B24" t="n">
-        <v>75188</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667799</v>
+        <v>667834</v>
       </c>
       <c r="R24" t="n">
-        <v>6700409</v>
+        <v>6700417</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3105,21 +3114,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3136,7 +3130,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753866</v>
+        <v>129753867</v>
       </c>
       <c r="B25" t="n">
         <v>98769</v>
@@ -3166,7 +3160,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3180,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667834</v>
+        <v>667764</v>
       </c>
       <c r="R25" t="n">
-        <v>6700417</v>
+        <v>6700442</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3242,54 +3236,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753867</v>
+        <v>129753870</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>75188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667764</v>
+        <v>667799</v>
       </c>
       <c r="R26" t="n">
-        <v>6700442</v>
+        <v>6700409</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3332,6 +3317,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,45 +2019,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B14" t="n">
-        <v>100958</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R14" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2116,50 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R15" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98747</v>
+        <v>98752</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129753866</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>129753867</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>129753870</v>
       </c>
       <c r="B26" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>101865</v>
+        <v>101870</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,54 +3557,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129753854</v>
+        <v>129753874</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>4779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667811</v>
+        <v>667806</v>
       </c>
       <c r="R29" t="n">
-        <v>6700403</v>
+        <v>6700465</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3647,6 +3638,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3663,45 +3669,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129753874</v>
+        <v>129753854</v>
       </c>
       <c r="B30" t="n">
-        <v>4779</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667806</v>
+        <v>667811</v>
       </c>
       <c r="R30" t="n">
-        <v>6700465</v>
+        <v>6700403</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3744,21 +3759,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,54 +3872,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129753868</v>
+        <v>129753872</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667748</v>
+        <v>667802</v>
       </c>
       <c r="R32" t="n">
-        <v>6700464</v>
+        <v>6700434</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3962,6 +3953,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3978,45 +3984,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129753872</v>
+        <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>4779</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667802</v>
+        <v>667748</v>
       </c>
       <c r="R33" t="n">
-        <v>6700434</v>
+        <v>6700464</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4059,21 +4074,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -3024,54 +3024,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753866</v>
+        <v>129753870</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>75193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667834</v>
+        <v>667799</v>
       </c>
       <c r="R24" t="n">
-        <v>6700417</v>
+        <v>6700409</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3114,6 +3105,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3130,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753867</v>
+        <v>129753866</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3160,7 +3166,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3174,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667764</v>
+        <v>667834</v>
       </c>
       <c r="R25" t="n">
-        <v>6700442</v>
+        <v>6700417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3236,45 +3242,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753870</v>
+        <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>75193</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667799</v>
+        <v>667764</v>
       </c>
       <c r="R26" t="n">
-        <v>6700409</v>
+        <v>6700442</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3317,21 +3332,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753873</v>
+        <v>129753845</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>101870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667793</v>
+        <v>667823</v>
       </c>
       <c r="R27" t="n">
-        <v>6700438</v>
+        <v>6700429</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,21 +3429,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3460,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B28" t="n">
-        <v>101870</v>
+        <v>4779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R28" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3541,6 +3526,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,50 +2019,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R14" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R15" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B20" t="n">
-        <v>97020</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R20" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,21 +2702,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2733,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>97020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R21" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2814,6 +2799,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3136,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753866</v>
+        <v>129753867</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667834</v>
+        <v>667764</v>
       </c>
       <c r="R25" t="n">
-        <v>6700417</v>
+        <v>6700442</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753867</v>
+        <v>129753866</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667764</v>
+        <v>667834</v>
       </c>
       <c r="R26" t="n">
-        <v>6700442</v>
+        <v>6700417</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>97020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R20" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,6 +2702,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2718,32 +2733,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>97020</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R21" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2799,21 +2814,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3136,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753867</v>
+        <v>129753866</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667764</v>
+        <v>667834</v>
       </c>
       <c r="R25" t="n">
-        <v>6700442</v>
+        <v>6700417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3242,7 +3242,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753866</v>
+        <v>129753867</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667834</v>
+        <v>667764</v>
       </c>
       <c r="R26" t="n">
-        <v>6700417</v>
+        <v>6700442</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98752</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,45 +3024,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753870</v>
+        <v>129753866</v>
       </c>
       <c r="B24" t="n">
-        <v>75193</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667799</v>
+        <v>667834</v>
       </c>
       <c r="R24" t="n">
-        <v>6700409</v>
+        <v>6700417</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3105,21 +3114,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3136,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753866</v>
+        <v>129753867</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3160,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3180,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667834</v>
+        <v>667764</v>
       </c>
       <c r="R25" t="n">
-        <v>6700417</v>
+        <v>6700442</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3242,54 +3236,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753867</v>
+        <v>129753870</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>75193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667764</v>
+        <v>667799</v>
       </c>
       <c r="R26" t="n">
-        <v>6700442</v>
+        <v>6700409</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3332,6 +3317,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B27" t="n">
-        <v>101870</v>
+        <v>4779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R27" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,6 +3429,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3445,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753873</v>
+        <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>4779</v>
+        <v>101874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667793</v>
+        <v>667823</v>
       </c>
       <c r="R28" t="n">
-        <v>6700438</v>
+        <v>6700429</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3526,21 +3541,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,45 +2019,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B14" t="n">
-        <v>100967</v>
+        <v>57733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R14" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2116,50 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>100969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R15" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,54 +3024,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753866</v>
+        <v>129753870</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>75193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667834</v>
+        <v>667799</v>
       </c>
       <c r="R24" t="n">
-        <v>6700417</v>
+        <v>6700409</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3114,6 +3105,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3130,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753867</v>
+        <v>129753866</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3166,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3174,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667764</v>
+        <v>667834</v>
       </c>
       <c r="R25" t="n">
-        <v>6700442</v>
+        <v>6700417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3236,45 +3242,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753870</v>
+        <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>75193</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667799</v>
+        <v>667764</v>
       </c>
       <c r="R26" t="n">
-        <v>6700409</v>
+        <v>6700442</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3317,21 +3332,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3463,7 +3463,7 @@
         <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>101874</v>
+        <v>101876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,50 +2019,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R14" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>100969</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R15" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B20" t="n">
-        <v>97026</v>
+        <v>100979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R20" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,21 +2702,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2733,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B21" t="n">
-        <v>100969</v>
+        <v>97036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R21" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2814,6 +2799,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98758</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129753866</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753873</v>
+        <v>129753845</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>101886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667793</v>
+        <v>667823</v>
       </c>
       <c r="R27" t="n">
-        <v>6700438</v>
+        <v>6700429</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,21 +3429,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3460,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B28" t="n">
-        <v>101876</v>
+        <v>4779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R28" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3541,6 +3526,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3557,45 +3557,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129753874</v>
+        <v>129753854</v>
       </c>
       <c r="B29" t="n">
-        <v>4779</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667806</v>
+        <v>667811</v>
       </c>
       <c r="R29" t="n">
-        <v>6700465</v>
+        <v>6700403</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3638,21 +3647,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3669,54 +3663,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129753854</v>
+        <v>129753874</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>4779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667811</v>
+        <v>667806</v>
       </c>
       <c r="R30" t="n">
-        <v>6700403</v>
+        <v>6700465</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3759,6 +3744,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,45 +2019,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B14" t="n">
-        <v>100979</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R14" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2116,50 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>100983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R15" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>100979</v>
+        <v>97040</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R20" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,6 +2702,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2718,32 +2733,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>97036</v>
+        <v>100983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R21" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2799,21 +2814,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129753870</v>
       </c>
       <c r="B24" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129753866</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B27" t="n">
-        <v>101886</v>
+        <v>4779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R27" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,6 +3429,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3445,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753873</v>
+        <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>4779</v>
+        <v>101890</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667793</v>
+        <v>667823</v>
       </c>
       <c r="R28" t="n">
-        <v>6700438</v>
+        <v>6700429</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3526,21 +3541,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3560,7 +3560,7 @@
         <v>129753854</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,45 +3872,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129753872</v>
+        <v>129753868</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667802</v>
+        <v>667748</v>
       </c>
       <c r="R32" t="n">
-        <v>6700434</v>
+        <v>6700464</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3953,21 +3962,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3984,54 +3978,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129753868</v>
+        <v>129753872</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>4779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667748</v>
+        <v>667802</v>
       </c>
       <c r="R33" t="n">
-        <v>6700464</v>
+        <v>6700434</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4074,6 +4059,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,50 +2019,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>100983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R14" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>100983</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R15" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B20" t="n">
-        <v>97040</v>
+        <v>100983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R20" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,21 +2702,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2733,32 +2718,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B21" t="n">
-        <v>100983</v>
+        <v>97040</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2768,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R21" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2814,6 +2799,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3557,54 +3557,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129753854</v>
+        <v>129753874</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>4779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667811</v>
+        <v>667806</v>
       </c>
       <c r="R29" t="n">
-        <v>6700403</v>
+        <v>6700465</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3647,6 +3638,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3663,45 +3669,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129753874</v>
+        <v>129753854</v>
       </c>
       <c r="B30" t="n">
-        <v>4779</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667806</v>
+        <v>667811</v>
       </c>
       <c r="R30" t="n">
-        <v>6700465</v>
+        <v>6700403</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3744,21 +3759,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3872,54 +3872,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129753868</v>
+        <v>129753872</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667748</v>
+        <v>667802</v>
       </c>
       <c r="R32" t="n">
-        <v>6700464</v>
+        <v>6700434</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3962,6 +3953,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3978,45 +3984,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129753872</v>
+        <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>4779</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667802</v>
+        <v>667748</v>
       </c>
       <c r="R33" t="n">
-        <v>6700434</v>
+        <v>6700464</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4059,21 +4074,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,45 +2019,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B14" t="n">
-        <v>100983</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R14" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2116,50 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>100983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R15" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>129753856</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>129753892</v>
       </c>
       <c r="B15" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753893</v>
+        <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>100983</v>
+        <v>97043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667832</v>
+        <v>667791</v>
       </c>
       <c r="R20" t="n">
-        <v>6700425</v>
+        <v>6700469</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2702,6 +2702,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2718,32 +2733,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>97040</v>
+        <v>100986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R21" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2799,21 +2814,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129753870</v>
       </c>
       <c r="B24" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129753866</v>
       </c>
       <c r="B25" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753873</v>
+        <v>129753845</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>101893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667793</v>
+        <v>667823</v>
       </c>
       <c r="R27" t="n">
-        <v>6700438</v>
+        <v>6700429</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,21 +3429,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3460,10 +3445,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B28" t="n">
-        <v>101890</v>
+        <v>4779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R28" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3541,6 +3526,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3557,45 +3557,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129753874</v>
+        <v>129753854</v>
       </c>
       <c r="B29" t="n">
-        <v>4779</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667806</v>
+        <v>667811</v>
       </c>
       <c r="R29" t="n">
-        <v>6700465</v>
+        <v>6700403</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3638,21 +3647,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3669,54 +3663,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129753854</v>
+        <v>129753874</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>4779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667811</v>
+        <v>667806</v>
       </c>
       <c r="R30" t="n">
-        <v>6700403</v>
+        <v>6700465</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3759,6 +3744,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3872,45 +3872,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129753872</v>
+        <v>129753868</v>
       </c>
       <c r="B32" t="n">
-        <v>4779</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667802</v>
+        <v>667748</v>
       </c>
       <c r="R32" t="n">
-        <v>6700434</v>
+        <v>6700464</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3953,21 +3962,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3984,54 +3978,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129753868</v>
+        <v>129753872</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>4779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667748</v>
+        <v>667802</v>
       </c>
       <c r="R33" t="n">
-        <v>6700464</v>
+        <v>6700434</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4074,6 +4059,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,50 +2019,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>100986</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R14" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>100986</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R15" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,45 +2019,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B14" t="n">
-        <v>100986</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R14" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2116,50 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>100987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R15" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96239</v>
+        <v>96240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129753866</v>
       </c>
       <c r="B25" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>129753867</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B27" t="n">
-        <v>101893</v>
+        <v>4779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3359,21 +3359,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R27" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,6 +3429,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3445,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753873</v>
+        <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>4779</v>
+        <v>101894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667793</v>
+        <v>667823</v>
       </c>
       <c r="R28" t="n">
-        <v>6700438</v>
+        <v>6700429</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3526,21 +3541,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>129753868</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -3557,54 +3557,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129753854</v>
+        <v>129753874</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>4779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667811</v>
+        <v>667806</v>
       </c>
       <c r="R29" t="n">
-        <v>6700403</v>
+        <v>6700465</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3647,6 +3638,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3663,45 +3669,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129753874</v>
+        <v>129753854</v>
       </c>
       <c r="B30" t="n">
-        <v>4779</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667806</v>
+        <v>667811</v>
       </c>
       <c r="R30" t="n">
-        <v>6700465</v>
+        <v>6700403</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3744,21 +3759,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3872,54 +3872,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129753868</v>
+        <v>129753872</v>
       </c>
       <c r="B32" t="n">
-        <v>98798</v>
+        <v>4779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667748</v>
+        <v>667802</v>
       </c>
       <c r="R32" t="n">
-        <v>6700464</v>
+        <v>6700434</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3962,6 +3953,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -3978,45 +3984,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129753872</v>
+        <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>4779</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667802</v>
+        <v>667748</v>
       </c>
       <c r="R33" t="n">
-        <v>6700434</v>
+        <v>6700464</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4059,21 +4074,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -2019,50 +2019,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753856</v>
+        <v>129753892</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>101004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667802</v>
+        <v>667814</v>
       </c>
       <c r="R14" t="n">
-        <v>6700466</v>
+        <v>6700444</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,45 +2116,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>100987</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R15" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2221,7 +2221,7 @@
         <v>129753891</v>
       </c>
       <c r="B16" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>129753895</v>
       </c>
       <c r="B17" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129753871</v>
       </c>
       <c r="B18" t="n">
-        <v>96240</v>
+        <v>96257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>129753859</v>
       </c>
       <c r="B19" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129753851</v>
       </c>
       <c r="B20" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129753860</v>
       </c>
       <c r="B22" t="n">
-        <v>98776</v>
+        <v>98793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129753890</v>
       </c>
       <c r="B23" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3024,45 +3024,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753870</v>
+        <v>129753866</v>
       </c>
       <c r="B24" t="n">
-        <v>75199</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667799</v>
+        <v>667834</v>
       </c>
       <c r="R24" t="n">
-        <v>6700409</v>
+        <v>6700417</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3105,21 +3114,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3136,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753866</v>
+        <v>129753867</v>
       </c>
       <c r="B25" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,7 +3160,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3180,10 +3174,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667834</v>
+        <v>667764</v>
       </c>
       <c r="R25" t="n">
-        <v>6700417</v>
+        <v>6700442</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3242,54 +3236,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753867</v>
+        <v>129753870</v>
       </c>
       <c r="B26" t="n">
-        <v>98798</v>
+        <v>75200</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667764</v>
+        <v>667799</v>
       </c>
       <c r="R26" t="n">
-        <v>6700442</v>
+        <v>6700409</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3332,6 +3317,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3463,7 +3463,7 @@
         <v>129753845</v>
       </c>
       <c r="B28" t="n">
-        <v>101894</v>
+        <v>101911</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>129753854</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>129753896</v>
       </c>
       <c r="B31" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 54215-2025 artfynd.xlsx
+++ b/artfynd/A 54215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73917551</v>
+        <v>73917549</v>
       </c>
       <c r="B11" t="n">
-        <v>96312</v>
+        <v>95511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>221944</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667723.2880134189</v>
+        <v>667787.5043657159</v>
       </c>
       <c r="R11" t="n">
-        <v>6700414.587504691</v>
+        <v>6700429.928621698</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73917560</v>
+        <v>73917551</v>
       </c>
       <c r="B12" t="n">
         <v>96312</v>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>667499.1095760721</v>
+        <v>667723.2880134189</v>
       </c>
       <c r="R12" t="n">
-        <v>6700482.403118859</v>
+        <v>6700414.587504691</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73917547</v>
+        <v>73917560</v>
       </c>
       <c r="B13" t="n">
-        <v>99398</v>
+        <v>96312</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>667787.5043657159</v>
+        <v>667499.1095760721</v>
       </c>
       <c r="R13" t="n">
-        <v>6700429.928621698</v>
+        <v>6700482.403118859</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,53 +2019,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129753856</v>
+        <v>73917547</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>99398</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyböle, Upl</t>
+          <t>Kalvmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667802</v>
+        <v>667787.5043657159</v>
       </c>
       <c r="R14" t="n">
-        <v>6700466</v>
+        <v>6700429.928621698</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,12 +2089,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2018-10-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2018-10-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,52 +2124,57 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Astrid Eklund, Martin Westberg, Adrian Rönnqvist, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129753892</v>
+        <v>129753856</v>
       </c>
       <c r="B15" t="n">
-        <v>101020</v>
+        <v>57738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>667814</v>
+        <v>667802</v>
       </c>
       <c r="R15" t="n">
-        <v>6700444</v>
+        <v>6700466</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2218,7 +2233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129753891</v>
+        <v>129753892</v>
       </c>
       <c r="B16" t="n">
         <v>101020</v>
@@ -2253,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>667765</v>
+        <v>667814</v>
       </c>
       <c r="R16" t="n">
-        <v>6700434</v>
+        <v>6700444</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2315,7 +2330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129753895</v>
+        <v>129753891</v>
       </c>
       <c r="B17" t="n">
         <v>101020</v>
@@ -2350,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>667848</v>
+        <v>667765</v>
       </c>
       <c r="R17" t="n">
-        <v>6700386</v>
+        <v>6700434</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2412,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129753871</v>
+        <v>129753895</v>
       </c>
       <c r="B18" t="n">
-        <v>96273</v>
+        <v>101020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>667785</v>
+        <v>667848</v>
       </c>
       <c r="R18" t="n">
-        <v>6700459</v>
+        <v>6700386</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2493,21 +2508,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129753859</v>
+        <v>129753871</v>
       </c>
       <c r="B19" t="n">
-        <v>98809</v>
+        <v>96273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>667807</v>
+        <v>667785</v>
       </c>
       <c r="R19" t="n">
-        <v>6700432</v>
+        <v>6700459</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2605,6 +2605,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2621,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129753893</v>
+        <v>129753859</v>
       </c>
       <c r="B20" t="n">
-        <v>101020</v>
+        <v>98809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>667832</v>
+        <v>667807</v>
       </c>
       <c r="R20" t="n">
-        <v>6700425</v>
+        <v>6700432</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2718,32 +2733,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129753851</v>
+        <v>129753893</v>
       </c>
       <c r="B21" t="n">
-        <v>97077</v>
+        <v>101020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2753,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>667791</v>
+        <v>667832</v>
       </c>
       <c r="R21" t="n">
-        <v>6700469</v>
+        <v>6700425</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2799,21 +2814,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2830,32 +2830,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129753860</v>
+        <v>129753851</v>
       </c>
       <c r="B22" t="n">
-        <v>98809</v>
+        <v>97077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>667843</v>
+        <v>667791</v>
       </c>
       <c r="R22" t="n">
-        <v>6700368</v>
+        <v>6700469</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2911,6 +2911,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2927,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129753890</v>
+        <v>129753860</v>
       </c>
       <c r="B23" t="n">
-        <v>101020</v>
+        <v>98809</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2938,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>667791</v>
+        <v>667843</v>
       </c>
       <c r="R23" t="n">
-        <v>6700438</v>
+        <v>6700368</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3024,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129753870</v>
+        <v>129753890</v>
       </c>
       <c r="B24" t="n">
-        <v>75201</v>
+        <v>101020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3035,21 +3050,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3059,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>667799</v>
+        <v>667791</v>
       </c>
       <c r="R24" t="n">
-        <v>6700409</v>
+        <v>6700438</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3105,21 +3120,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3136,54 +3136,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129753866</v>
+        <v>129753870</v>
       </c>
       <c r="B25" t="n">
-        <v>98831</v>
+        <v>75201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>667834</v>
+        <v>667799</v>
       </c>
       <c r="R25" t="n">
-        <v>6700417</v>
+        <v>6700409</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3226,6 +3217,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3242,7 +3248,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129753867</v>
+        <v>129753866</v>
       </c>
       <c r="B26" t="n">
         <v>98831</v>
@@ -3272,7 +3278,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3286,10 +3292,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>667764</v>
+        <v>667834</v>
       </c>
       <c r="R26" t="n">
-        <v>6700442</v>
+        <v>6700417</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3348,45 +3354,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129753873</v>
+        <v>129753867</v>
       </c>
       <c r="B27" t="n">
-        <v>4779</v>
+        <v>98831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>667793</v>
+        <v>667764</v>
       </c>
       <c r="R27" t="n">
-        <v>6700438</v>
+        <v>6700442</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3429,21 +3444,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3460,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129753845</v>
+        <v>129753873</v>
       </c>
       <c r="B28" t="n">
-        <v>101927</v>
+        <v>4779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>667823</v>
+        <v>667793</v>
       </c>
       <c r="R28" t="n">
-        <v>6700429</v>
+        <v>6700438</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3541,6 +3541,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3557,54 +3572,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129753854</v>
+        <v>129753845</v>
       </c>
       <c r="B29" t="n">
-        <v>57900</v>
+        <v>101927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>667811</v>
+        <v>667823</v>
       </c>
       <c r="R29" t="n">
-        <v>6700403</v>
+        <v>6700429</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3663,45 +3669,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129753874</v>
+        <v>129753854</v>
       </c>
       <c r="B30" t="n">
-        <v>4779</v>
+        <v>57900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>667806</v>
+        <v>667811</v>
       </c>
       <c r="R30" t="n">
-        <v>6700465</v>
+        <v>6700403</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3744,21 +3759,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3775,10 +3775,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129753896</v>
+        <v>129753874</v>
       </c>
       <c r="B31" t="n">
-        <v>101020</v>
+        <v>4779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3786,21 +3786,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>667762</v>
+        <v>667806</v>
       </c>
       <c r="R31" t="n">
-        <v>6700443</v>
+        <v>6700465</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3856,6 +3856,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3872,54 +3887,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129753868</v>
+        <v>129753896</v>
       </c>
       <c r="B32" t="n">
-        <v>98831</v>
+        <v>101020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>667748</v>
+        <v>667762</v>
       </c>
       <c r="R32" t="n">
-        <v>6700464</v>
+        <v>6700443</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3978,45 +3984,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129753872</v>
+        <v>129753868</v>
       </c>
       <c r="B33" t="n">
-        <v>4779</v>
+        <v>98831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nyböle, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>667802</v>
+        <v>667748</v>
       </c>
       <c r="R33" t="n">
-        <v>6700434</v>
+        <v>6700464</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4060,21 +4075,6 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
@@ -4087,6 +4087,118 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129753872</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nyböle, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>667802</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6700434</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
